--- a/data/trans_bre/IQ2605_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IQ2605_R2-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,8</t>
+          <t>-12,18</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-2,26%</t>
+          <t>-14,5%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 10,92</t>
+          <t>-14,17; 9,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 8,98</t>
+          <t>-13,1; 9,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 7,93</t>
+          <t>-15,31; 8,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-32,35; 29,04</t>
+          <t>-41,21; 14,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,56; 24,17</t>
+          <t>-24,38; 21,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 13,58</t>
+          <t>-16,07; 13,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,86; 10,44</t>
+          <t>-17,6; 11,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-37,1; 50,27</t>
+          <t>-48,11; 18,8</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-7,38</t>
+          <t>-7,28</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-9,58%</t>
+          <t>-9,52%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 8,96</t>
+          <t>-2,35; 8,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 4,09</t>
+          <t>-5,19; 4,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 2,14</t>
+          <t>-7,2; 1,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,21; 3,47</t>
+          <t>-17,35; 3,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 18,53</t>
+          <t>-4,36; 17,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 5,73</t>
+          <t>-6,78; 6,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 2,79</t>
+          <t>-9,01; 2,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,6; 4,72</t>
+          <t>-21,83; 5,49</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>1,47</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 5,88</t>
+          <t>-12,47; 4,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 11,69</t>
+          <t>-4,01; 11,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 2,62</t>
+          <t>-13,23; 2,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 16,91</t>
+          <t>-12,88; 19,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,44; 10,75</t>
+          <t>-19,67; 9,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 17,3</t>
+          <t>-5,3; 17,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 3,34</t>
+          <t>-15,43; 3,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 26,51</t>
+          <t>-16,0; 31,58</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-4,45</t>
+          <t>-5,11</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-5,83%</t>
+          <t>-6,69%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 5,35</t>
+          <t>-3,03; 5,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 4,44</t>
+          <t>-3,42; 4,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 0,25</t>
+          <t>-6,86; 0,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 3,92</t>
+          <t>-13,23; 3,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 10,42</t>
+          <t>-5,53; 10,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 6,16</t>
+          <t>-4,55; 6,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 0,31</t>
+          <t>-8,46; 0,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,02; 5,25</t>
+          <t>-16,57; 4,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ2605_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IQ2605_R2-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-2,4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,13</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,83</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-12,18</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-4,62%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-1,54%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-3,45%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-14,5%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-2.400042502426758</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.128834540437629</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-2.833583272297102</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-12.17709528360033</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.0461647088024668</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.01536078402387187</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.03446651773705895</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.1450460094373388</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-14,17; 9,79</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-13,1; 9,11</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-15,31; 8,66</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-41,21; 14,71</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-24,38; 21,94</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-16,07; 13,54</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-17,6; 11,36</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-48,11; 18,8</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-14.17156005341335</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-13.10109767732675</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-15.31420058894862</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-41.21211174536971</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2438450919910874</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.1607148055408527</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.1760190799058367</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.4811053449844386</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>9.793326339715971</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9.109373318193001</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8.660633253717739</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>14.70516768405879</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.2194369146805636</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.1353651228894865</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.113582860567392</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.1880123155173182</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3,21</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,66</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-7,28</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-0,79%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-3,41%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-9,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,35; 8,42</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,19; 4,78</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-7,2; 1,72</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-17,35; 3,88</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-4,36; 17,72</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-6,78; 6,7</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-9,01; 2,31</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-21,83; 5,49</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>3.21053828497968</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.5826271632021318</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-2.663647429500993</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-7.281572327347952</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.06294903632149629</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.007888920356991118</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.03408714846698774</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.09518420780655389</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,1</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,05</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,46</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-5,27%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-5,53%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.348365323451874</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.188934488297278</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-7.203036114158078</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-17.3501791512945</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.04362587011282255</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.06782803915579251</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.09006964707465596</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.2182886972004368</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-12,47; 4,99</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,01; 11,94</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-13,23; 2,36</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-12,88; 19,83</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-19,67; 9,38</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-5,3; 17,87</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-15,43; 3,06</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-16,0; 31,58</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>8.417586179147731</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.784592708206998</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.720632472038324</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.875808689336509</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1771701687642476</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.06701265606160101</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.02305849726351869</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.05489405044827905</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,15</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-3,16</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-5,11</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-3,99%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-6,69%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-3.095343275313256</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>4.04638704705178</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-4.46387243212063</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.472603004613215</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.05273030670944172</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.05684708491617693</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.05525639883882214</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.01998041908236755</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,03; 5,51</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,42; 4,49</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-6,86; 0,09</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-13,23; 3,42</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-5,53; 10,92</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-4,55; 6,27</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-8,46; 0,17</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-16,57; 4,65</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-12.47075544682457</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.009615339380543</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-13.22892342970005</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-12.87915513413359</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1967241154871823</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.05298088304271124</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.154283329287937</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.1600423821528316</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.992401236033231</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>11.93741626983452</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.355103981042038</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>19.82501910812487</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.09375276926184993</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.1787438849626233</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.03058535898371835</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.3157543684798684</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.15459386913298</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.397383265820217</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-3.159160033088659</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-5.107941800459526</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.02186961617195119</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.005428174395056689</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.0399014313013596</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.06690871548552733</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.030863434208423</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.420298647903398</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-6.859868753305517</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-13.23146662025233</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.0552516208546141</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.04554475819606173</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.08455027958582431</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.1656696221126695</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.505065666667925</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.494050769541853</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.0948525551437846</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3.424689944129816</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1092100037296886</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.0627203138335559</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.001694597755322028</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.04646814411696432</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
